--- a/data/nzd0329/nzd0329.xlsx
+++ b/data/nzd0329/nzd0329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O529"/>
+  <dimension ref="A1:O533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27290,6 +27290,210 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:34+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>408.22</v>
+      </c>
+      <c r="C530" t="n">
+        <v>365.14</v>
+      </c>
+      <c r="D530" t="n">
+        <v>316.78</v>
+      </c>
+      <c r="E530" t="n">
+        <v>315.43</v>
+      </c>
+      <c r="F530" t="n">
+        <v>391.11</v>
+      </c>
+      <c r="G530" t="n">
+        <v>382.21</v>
+      </c>
+      <c r="H530" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="I530" t="n">
+        <v>374.07</v>
+      </c>
+      <c r="J530" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="K530" t="n">
+        <v>396.84</v>
+      </c>
+      <c r="L530" t="n">
+        <v>403.43</v>
+      </c>
+      <c r="M530" t="n">
+        <v>397.02</v>
+      </c>
+      <c r="N530" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>408.22</v>
+      </c>
+      <c r="C531" t="n">
+        <v>360.71</v>
+      </c>
+      <c r="D531" t="n">
+        <v>311.08</v>
+      </c>
+      <c r="E531" t="n">
+        <v>310.11</v>
+      </c>
+      <c r="F531" t="n">
+        <v>391.11</v>
+      </c>
+      <c r="G531" t="n">
+        <v>382.21</v>
+      </c>
+      <c r="H531" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="I531" t="n">
+        <v>374.07</v>
+      </c>
+      <c r="J531" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="K531" t="n">
+        <v>396.84</v>
+      </c>
+      <c r="L531" t="n">
+        <v>403.43</v>
+      </c>
+      <c r="M531" t="n">
+        <v>397.02</v>
+      </c>
+      <c r="N531" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:18:39+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>406.08</v>
+      </c>
+      <c r="C532" t="n">
+        <v>358.82</v>
+      </c>
+      <c r="D532" t="n">
+        <v>300.99</v>
+      </c>
+      <c r="E532" t="n">
+        <v>300.02</v>
+      </c>
+      <c r="F532" t="n">
+        <v>390.25</v>
+      </c>
+      <c r="G532" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="H532" t="n">
+        <v>279.96</v>
+      </c>
+      <c r="I532" t="n">
+        <v>371.33</v>
+      </c>
+      <c r="J532" t="n">
+        <v>382.08</v>
+      </c>
+      <c r="K532" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="L532" t="n">
+        <v>404.06</v>
+      </c>
+      <c r="M532" t="n">
+        <v>398.57</v>
+      </c>
+      <c r="N532" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>407.61</v>
+      </c>
+      <c r="C533" t="n">
+        <v>359.09</v>
+      </c>
+      <c r="D533" t="n">
+        <v>297.13</v>
+      </c>
+      <c r="E533" t="n">
+        <v>296.77</v>
+      </c>
+      <c r="F533" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="G533" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="H533" t="n">
+        <v>279.96</v>
+      </c>
+      <c r="I533" t="n">
+        <v>371.33</v>
+      </c>
+      <c r="J533" t="n">
+        <v>382.08</v>
+      </c>
+      <c r="K533" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="L533" t="n">
+        <v>404.06</v>
+      </c>
+      <c r="M533" t="n">
+        <v>398.57</v>
+      </c>
+      <c r="N533" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27301,7 +27505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B553"/>
+  <dimension ref="A1:B557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32834,6 +33038,46 @@
       </c>
       <c r="B553" t="n">
         <v>-0.22</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -33002,28 +33246,28 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.378531037242996</v>
+        <v>-1.368718185369652</v>
       </c>
       <c r="J2" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K2" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5262562900959735</v>
+        <v>0.5253565616419902</v>
       </c>
       <c r="M2" t="n">
-        <v>7.912232002063799</v>
+        <v>7.884708701139039</v>
       </c>
       <c r="N2" t="n">
-        <v>106.1653004119393</v>
+        <v>105.78021910061</v>
       </c>
       <c r="O2" t="n">
-        <v>10.30365471140892</v>
+        <v>10.28495109860081</v>
       </c>
       <c r="P2" t="n">
-        <v>437.1750861290079</v>
+        <v>437.0744026646794</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33080,28 +33324,28 @@
         <v>0.0912</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.381978432971564</v>
+        <v>-1.410770928839806</v>
       </c>
       <c r="J3" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K3" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3888426097642891</v>
+        <v>0.3975914214270102</v>
       </c>
       <c r="M3" t="n">
-        <v>10.54859735673833</v>
+        <v>10.6450524768775</v>
       </c>
       <c r="N3" t="n">
-        <v>187.3694193519602</v>
+        <v>189.5553934531187</v>
       </c>
       <c r="O3" t="n">
-        <v>13.68829497607208</v>
+        <v>13.76791173174489</v>
       </c>
       <c r="P3" t="n">
-        <v>420.0896806702435</v>
+        <v>420.3837957940564</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33158,28 +33402,28 @@
         <v>0.081</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.60625917716103</v>
+        <v>-1.676116133221269</v>
       </c>
       <c r="J4" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K4" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1029980519824513</v>
+        <v>0.1110666325457182</v>
       </c>
       <c r="M4" t="n">
-        <v>29.84246313077564</v>
+        <v>30.07226202717838</v>
       </c>
       <c r="N4" t="n">
-        <v>1406.544050347524</v>
+        <v>1417.360659100586</v>
       </c>
       <c r="O4" t="n">
-        <v>37.50392046636624</v>
+        <v>37.64785065711701</v>
       </c>
       <c r="P4" t="n">
-        <v>403.0200515276786</v>
+        <v>403.7330413262828</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33236,28 +33480,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.280106520625804</v>
+        <v>-2.336676480797145</v>
       </c>
       <c r="J5" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K5" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1952355329888452</v>
+        <v>0.2037285934261166</v>
       </c>
       <c r="M5" t="n">
-        <v>28.94231568167413</v>
+        <v>29.09030758559629</v>
       </c>
       <c r="N5" t="n">
-        <v>1306.970399375806</v>
+        <v>1310.675574629495</v>
       </c>
       <c r="O5" t="n">
-        <v>36.15204557664485</v>
+        <v>36.20325364700658</v>
       </c>
       <c r="P5" t="n">
-        <v>409.0629498352688</v>
+        <v>409.6531675841528</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33314,28 +33558,28 @@
         <v>0.0479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8265572348291973</v>
+        <v>-0.8169966607871352</v>
       </c>
       <c r="J6" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K6" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06127466148182958</v>
+        <v>0.0606883689072808</v>
       </c>
       <c r="M6" t="n">
-        <v>15.59172135375245</v>
+        <v>15.52714379588605</v>
       </c>
       <c r="N6" t="n">
-        <v>638.334653659175</v>
+        <v>634.4003743448975</v>
       </c>
       <c r="O6" t="n">
-        <v>25.26528554477814</v>
+        <v>25.18730581751247</v>
       </c>
       <c r="P6" t="n">
-        <v>400.7463344610885</v>
+        <v>400.6463056186492</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33392,28 +33636,28 @@
         <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7351459234962794</v>
+        <v>-0.7343541628010241</v>
       </c>
       <c r="J7" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K7" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1430234348825171</v>
+        <v>0.1445504627810249</v>
       </c>
       <c r="M7" t="n">
-        <v>8.246726413023744</v>
+        <v>8.188358278090437</v>
       </c>
       <c r="N7" t="n">
-        <v>201.2738470938907</v>
+        <v>199.7439346785457</v>
       </c>
       <c r="O7" t="n">
-        <v>14.18710143383386</v>
+        <v>14.13307944782544</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0282997803439</v>
+        <v>401.0201627167557</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33470,28 +33714,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.105524441085617</v>
+        <v>-1.220296247999383</v>
       </c>
       <c r="J8" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K8" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3016010269764938</v>
+        <v>0.2877443997726868</v>
       </c>
       <c r="M8" t="n">
-        <v>8.338867338305553</v>
+        <v>9.27413635066199</v>
       </c>
       <c r="N8" t="n">
-        <v>174.3743193625477</v>
+        <v>228.7047519096334</v>
       </c>
       <c r="O8" t="n">
-        <v>13.20508687447938</v>
+        <v>15.12298753254903</v>
       </c>
       <c r="P8" t="n">
-        <v>401.5822125537202</v>
+        <v>402.7691462236313</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33548,28 +33792,28 @@
         <v>0.1418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9236922732818832</v>
+        <v>-0.918506913856915</v>
       </c>
       <c r="J9" t="n">
+        <v>532</v>
+      </c>
+      <c r="K9" t="n">
         <v>528</v>
       </c>
-      <c r="K9" t="n">
-        <v>524</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.4175706018838818</v>
+        <v>0.4179627903058009</v>
       </c>
       <c r="M9" t="n">
-        <v>6.140697439192214</v>
+        <v>6.120351835060291</v>
       </c>
       <c r="N9" t="n">
-        <v>73.66405237981772</v>
+        <v>73.23372164209847</v>
       </c>
       <c r="O9" t="n">
-        <v>8.582776495972485</v>
+        <v>8.55767033964843</v>
       </c>
       <c r="P9" t="n">
-        <v>393.6307567355855</v>
+        <v>393.5773904223249</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33626,28 +33870,28 @@
         <v>0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8103010616157436</v>
+        <v>-0.7927438304425637</v>
       </c>
       <c r="J10" t="n">
+        <v>532</v>
+      </c>
+      <c r="K10" t="n">
         <v>528</v>
       </c>
-      <c r="K10" t="n">
-        <v>524</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.3682157631141806</v>
+        <v>0.3571327303928992</v>
       </c>
       <c r="M10" t="n">
-        <v>6.269817974806777</v>
+        <v>6.314602216847137</v>
       </c>
       <c r="N10" t="n">
-        <v>69.73436296737067</v>
+        <v>70.51646255998399</v>
       </c>
       <c r="O10" t="n">
-        <v>8.350710327114136</v>
+        <v>8.397408085831247</v>
       </c>
       <c r="P10" t="n">
-        <v>391.4442391650621</v>
+        <v>391.2634880570211</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33704,28 +33948,28 @@
         <v>0.0985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8494328838249924</v>
+        <v>-0.8267593072991671</v>
       </c>
       <c r="J11" t="n">
+        <v>532</v>
+      </c>
+      <c r="K11" t="n">
         <v>528</v>
       </c>
-      <c r="K11" t="n">
-        <v>524</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2784557525194946</v>
+        <v>0.2669016080704422</v>
       </c>
       <c r="M11" t="n">
-        <v>8.344365848531748</v>
+        <v>8.407458379410464</v>
       </c>
       <c r="N11" t="n">
-        <v>115.7317516321314</v>
+        <v>117.0313937819458</v>
       </c>
       <c r="O11" t="n">
-        <v>10.75786928867103</v>
+        <v>10.81810490714274</v>
       </c>
       <c r="P11" t="n">
-        <v>402.5110659524281</v>
+        <v>402.2776265058629</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33782,28 +34026,28 @@
         <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9420856870932781</v>
+        <v>-0.9143652470518032</v>
       </c>
       <c r="J12" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K12" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2710761298164163</v>
+        <v>0.2580653263956766</v>
       </c>
       <c r="M12" t="n">
-        <v>9.638673284833724</v>
+        <v>9.702019029814547</v>
       </c>
       <c r="N12" t="n">
-        <v>147.1720760313425</v>
+        <v>149.2777149177131</v>
       </c>
       <c r="O12" t="n">
-        <v>12.13144987342166</v>
+        <v>12.21792596628876</v>
       </c>
       <c r="P12" t="n">
-        <v>408.2731905207748</v>
+        <v>407.9870238718069</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33860,28 +34104,28 @@
         <v>0.137</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6983657952202896</v>
+        <v>-0.6711336526174073</v>
       </c>
       <c r="J13" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K13" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1854798254841922</v>
+        <v>0.1724751613251571</v>
       </c>
       <c r="M13" t="n">
-        <v>8.828268991813562</v>
+        <v>8.889570991103223</v>
       </c>
       <c r="N13" t="n">
-        <v>131.7705470517232</v>
+        <v>133.8901107668628</v>
       </c>
       <c r="O13" t="n">
-        <v>11.4791352919862</v>
+        <v>11.57108943733747</v>
       </c>
       <c r="P13" t="n">
-        <v>396.1307608725444</v>
+        <v>395.848616929695</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33938,28 +34182,28 @@
         <v>0.1005</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8486558421045337</v>
+        <v>-0.8227082430866598</v>
       </c>
       <c r="J14" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="K14" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2870133601304495</v>
+        <v>0.2722708405300528</v>
       </c>
       <c r="M14" t="n">
-        <v>8.189003734074866</v>
+        <v>8.271410865965761</v>
       </c>
       <c r="N14" t="n">
-        <v>110.7409690064953</v>
+        <v>112.7576017025224</v>
       </c>
       <c r="O14" t="n">
-        <v>10.52335350572693</v>
+        <v>10.61873823495628</v>
       </c>
       <c r="P14" t="n">
-        <v>398.4464288302571</v>
+        <v>398.1787874475272</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33997,7 +34241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O529"/>
+  <dimension ref="A1:O533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74441,6 +74685,314 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:34+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-40.95751540605107,172.10033584125526</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-40.956772798414015,172.10064621539266</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-40.95602042110994,172.10101797808085</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-40.955354950014566,172.10084306968372</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-40.954831882886,172.0997724187385</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-40.954152439943705,172.09968531289627</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-40.953320910745944,172.10055474448882</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-40.952806606661085,172.09939767392873</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-40.952138687630026,172.09913269696995</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-40.95146672731745,172.0988819152594</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-40.95079790469339,172.09870916394306</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>-40.95011752378497,172.09869010865606</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>-40.94944030818596,172.09862884539555</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:18:43+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-40.95751540605107,172.10033584125526</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-40.956764608270724,172.10069773111977</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-40.95600988273928,172.1010842616029</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-40.95534511425682,172.100904933697</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-40.954831882886,172.0997724187385</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-40.954152439943705,172.09968531289627</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-40.953320910745944,172.10055474448882</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-40.952806606661085,172.09939767392873</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-40.952138687630026,172.09913269696995</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-40.95146672731745,172.0988819152594</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-40.95079790469339,172.09870916394306</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-40.95011752378497,172.09869010865606</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>-40.94944030818596,172.09862884539555</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:18:39+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-40.957511449725445,172.10036072725867</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-40.95676111404904,172.10071970960908</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-40.95599122788035,172.10120159501548</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-40.955326459504235,172.10102226595896</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-40.95483029298421,172.09978241925666</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-40.954151090376826,172.09969380162133</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-40.95330040729033,172.10068370140996</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-40.952802108820805,172.09942968294104</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>-40.9521367483835,172.09915237260773</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>-40.95146664734545,172.0988829793194</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-40.95079846448875,172.09870171559737</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>-40.95011890106217,172.09867178354958</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>-40.94944208531346,172.09860520033806</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-40.957514278313944,172.10034293492942</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-40.95676161322381,172.10071656982504</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-40.955984091301936,172.10124648171535</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-40.9553204507625,172.10106005879481</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-40.954792782141226,172.10001836157895</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-40.954151090376826,172.09969380162133</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-40.95330040729033,172.10068370140996</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-40.952802108820805,172.09942968294104</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>-40.9521367483835,172.09915237260773</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>-40.95146664734545,172.0988829793194</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-40.95079846448875,172.09870171559737</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-40.95011890106217,172.09867178354958</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>-40.94944208531346,172.09860520033806</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0329/nzd0329.xlsx
+++ b/data/nzd0329/nzd0329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O533"/>
+  <dimension ref="A1:O537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27462,7 +27462,7 @@
         <v>296.77</v>
       </c>
       <c r="F533" t="n">
-        <v>369.96</v>
+        <v>390.25</v>
       </c>
       <c r="G533" t="n">
         <v>381.48</v>
@@ -27489,6 +27489,210 @@
         <v>396.18</v>
       </c>
       <c r="O533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:59+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>408.9</v>
+      </c>
+      <c r="C534" t="n">
+        <v>357.66</v>
+      </c>
+      <c r="D534" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="E534" t="n">
+        <v>294.33</v>
+      </c>
+      <c r="F534" t="n">
+        <v>390.25</v>
+      </c>
+      <c r="G534" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="H534" t="n">
+        <v>279.96</v>
+      </c>
+      <c r="I534" t="n">
+        <v>371.33</v>
+      </c>
+      <c r="J534" t="n">
+        <v>382.08</v>
+      </c>
+      <c r="K534" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="L534" t="n">
+        <v>404.06</v>
+      </c>
+      <c r="M534" t="n">
+        <v>398.57</v>
+      </c>
+      <c r="N534" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>407.55</v>
+      </c>
+      <c r="C535" t="n">
+        <v>357.82</v>
+      </c>
+      <c r="D535" t="n">
+        <v>284.67</v>
+      </c>
+      <c r="E535" t="n">
+        <v>284.65</v>
+      </c>
+      <c r="F535" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="G535" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="H535" t="n">
+        <v>265.49</v>
+      </c>
+      <c r="I535" t="n">
+        <v>368.36</v>
+      </c>
+      <c r="J535" t="n">
+        <v>380.19</v>
+      </c>
+      <c r="K535" t="n">
+        <v>396.48</v>
+      </c>
+      <c r="L535" t="n">
+        <v>406.01</v>
+      </c>
+      <c r="M535" t="n">
+        <v>401.9</v>
+      </c>
+      <c r="N535" t="n">
+        <v>400.88</v>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>407.47</v>
+      </c>
+      <c r="C536" t="n">
+        <v>358.59</v>
+      </c>
+      <c r="D536" t="n">
+        <v>285.58</v>
+      </c>
+      <c r="E536" t="n">
+        <v>285.22</v>
+      </c>
+      <c r="F536" t="n">
+        <v>387.95</v>
+      </c>
+      <c r="G536" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="H536" t="n">
+        <v>252.37</v>
+      </c>
+      <c r="I536" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="J536" t="n">
+        <v>378.56</v>
+      </c>
+      <c r="K536" t="n">
+        <v>395.98</v>
+      </c>
+      <c r="L536" t="n">
+        <v>409.02</v>
+      </c>
+      <c r="M536" t="n">
+        <v>404.34</v>
+      </c>
+      <c r="N536" t="n">
+        <v>402.83</v>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>407.27</v>
+      </c>
+      <c r="C537" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="D537" t="n">
+        <v>290.85</v>
+      </c>
+      <c r="E537" t="n">
+        <v>289.77</v>
+      </c>
+      <c r="F537" t="n">
+        <v>384.67</v>
+      </c>
+      <c r="G537" t="n">
+        <v>376.26</v>
+      </c>
+      <c r="H537" t="n">
+        <v>228.72</v>
+      </c>
+      <c r="I537" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="J537" t="n">
+        <v>378.56</v>
+      </c>
+      <c r="K537" t="n">
+        <v>395.98</v>
+      </c>
+      <c r="L537" t="n">
+        <v>403.01</v>
+      </c>
+      <c r="M537" t="n">
+        <v>404.34</v>
+      </c>
+      <c r="N537" t="n">
+        <v>402.83</v>
+      </c>
+      <c r="O537" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27505,7 +27709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B557"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33078,6 +33282,46 @@
       </c>
       <c r="B557" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -33246,28 +33490,28 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.368718185369652</v>
+        <v>-1.358794225572409</v>
       </c>
       <c r="J2" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K2" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5253565616419902</v>
+        <v>0.5242893961790149</v>
       </c>
       <c r="M2" t="n">
-        <v>7.884708701139039</v>
+        <v>7.857867828188436</v>
       </c>
       <c r="N2" t="n">
-        <v>105.78021910061</v>
+        <v>105.420405673125</v>
       </c>
       <c r="O2" t="n">
-        <v>10.28495109860081</v>
+        <v>10.26744396980695</v>
       </c>
       <c r="P2" t="n">
-        <v>437.0744026646794</v>
+        <v>436.9722039743718</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33324,28 +33568,28 @@
         <v>0.0912</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.410770928839806</v>
+        <v>-1.441135398900377</v>
       </c>
       <c r="J3" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K3" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3975914214270102</v>
+        <v>0.4061489131977896</v>
       </c>
       <c r="M3" t="n">
-        <v>10.6450524768775</v>
+        <v>10.7549611916624</v>
       </c>
       <c r="N3" t="n">
-        <v>189.5553934531187</v>
+        <v>192.1966846983071</v>
       </c>
       <c r="O3" t="n">
-        <v>13.76791173174489</v>
+        <v>13.86350189159676</v>
       </c>
       <c r="P3" t="n">
-        <v>420.3837957940564</v>
+        <v>420.6950653180042</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33402,28 +33646,28 @@
         <v>0.081</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.676116133221269</v>
+        <v>-1.766008770558691</v>
       </c>
       <c r="J4" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K4" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1110666325457182</v>
+        <v>0.1206662840999545</v>
       </c>
       <c r="M4" t="n">
-        <v>30.07226202717838</v>
+        <v>30.4327530861603</v>
       </c>
       <c r="N4" t="n">
-        <v>1417.360659100586</v>
+        <v>1442.421499693276</v>
       </c>
       <c r="O4" t="n">
-        <v>37.64785065711701</v>
+        <v>37.9792245799368</v>
       </c>
       <c r="P4" t="n">
-        <v>403.7330413262828</v>
+        <v>404.6538274096885</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33480,28 +33724,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.336676480797145</v>
+        <v>-2.413498851311191</v>
       </c>
       <c r="J5" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K5" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2037285934261166</v>
+        <v>0.213628946675459</v>
       </c>
       <c r="M5" t="n">
-        <v>29.09030758559629</v>
+        <v>29.37311598537555</v>
       </c>
       <c r="N5" t="n">
-        <v>1310.675574629495</v>
+        <v>1325.9160947862</v>
       </c>
       <c r="O5" t="n">
-        <v>36.20325364700658</v>
+        <v>36.41313080176161</v>
       </c>
       <c r="P5" t="n">
-        <v>409.6531675841528</v>
+        <v>410.4575036704941</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33558,28 +33802,28 @@
         <v>0.0479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8169966607871352</v>
+        <v>-0.7982482708913925</v>
       </c>
       <c r="J6" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K6" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0606883689072808</v>
+        <v>0.05882213742168318</v>
       </c>
       <c r="M6" t="n">
-        <v>15.52714379588605</v>
+        <v>15.41937659993174</v>
       </c>
       <c r="N6" t="n">
-        <v>634.4003743448975</v>
+        <v>630.2636572398737</v>
       </c>
       <c r="O6" t="n">
-        <v>25.18730581751247</v>
+        <v>25.10505242455936</v>
       </c>
       <c r="P6" t="n">
-        <v>400.6463056186492</v>
+        <v>400.4493435135577</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33636,28 +33880,28 @@
         <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7343541628010241</v>
+        <v>-0.736078731548425</v>
       </c>
       <c r="J7" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K7" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1445504627810249</v>
+        <v>0.1468880222350423</v>
       </c>
       <c r="M7" t="n">
-        <v>8.188358278090437</v>
+        <v>8.140582543914313</v>
       </c>
       <c r="N7" t="n">
-        <v>199.7439346785457</v>
+        <v>198.2841366696614</v>
       </c>
       <c r="O7" t="n">
-        <v>14.13307944782544</v>
+        <v>14.08134001683296</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0201627167557</v>
+        <v>401.0379828745683</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33714,28 +33958,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.220296247999383</v>
+        <v>-1.368567576230809</v>
       </c>
       <c r="J8" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K8" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2877443997726868</v>
+        <v>0.2651531960071511</v>
       </c>
       <c r="M8" t="n">
-        <v>9.27413635066199</v>
+        <v>10.65122600140438</v>
       </c>
       <c r="N8" t="n">
-        <v>228.7047519096334</v>
+        <v>324.2733413948429</v>
       </c>
       <c r="O8" t="n">
-        <v>15.12298753254903</v>
+        <v>18.00759121578572</v>
       </c>
       <c r="P8" t="n">
-        <v>402.7691462236313</v>
+        <v>404.3084327794651</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33792,28 +34036,28 @@
         <v>0.1418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.918506913856915</v>
+        <v>-0.9201402408640297</v>
       </c>
       <c r="J9" t="n">
+        <v>536</v>
+      </c>
+      <c r="K9" t="n">
         <v>532</v>
       </c>
-      <c r="K9" t="n">
-        <v>528</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.4179627903058009</v>
+        <v>0.4219851677122674</v>
       </c>
       <c r="M9" t="n">
-        <v>6.120351835060291</v>
+        <v>6.094076249312366</v>
       </c>
       <c r="N9" t="n">
-        <v>73.23372164209847</v>
+        <v>72.78655041741472</v>
       </c>
       <c r="O9" t="n">
-        <v>8.55767033964843</v>
+        <v>8.531503408978672</v>
       </c>
       <c r="P9" t="n">
-        <v>393.5773904223249</v>
+        <v>393.5943183272612</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33870,28 +34114,28 @@
         <v>0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7927438304425637</v>
+        <v>-0.7797571028770179</v>
       </c>
       <c r="J10" t="n">
+        <v>536</v>
+      </c>
+      <c r="K10" t="n">
         <v>532</v>
       </c>
-      <c r="K10" t="n">
-        <v>528</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.3571327303928992</v>
+        <v>0.3504421149224475</v>
       </c>
       <c r="M10" t="n">
-        <v>6.314602216847137</v>
+        <v>6.334692315675383</v>
       </c>
       <c r="N10" t="n">
-        <v>70.51646255998399</v>
+        <v>70.73291193791948</v>
       </c>
       <c r="O10" t="n">
-        <v>8.397408085831247</v>
+        <v>8.41028607943389</v>
       </c>
       <c r="P10" t="n">
-        <v>391.2634880570211</v>
+        <v>391.1293108876203</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33948,28 +34192,28 @@
         <v>0.0985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8267593072991671</v>
+        <v>-0.8054854691010038</v>
       </c>
       <c r="J11" t="n">
+        <v>536</v>
+      </c>
+      <c r="K11" t="n">
         <v>532</v>
       </c>
-      <c r="K11" t="n">
-        <v>528</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.2669016080704422</v>
+        <v>0.2563733702096579</v>
       </c>
       <c r="M11" t="n">
-        <v>8.407458379410464</v>
+        <v>8.46402359427422</v>
       </c>
       <c r="N11" t="n">
-        <v>117.0313937819458</v>
+        <v>118.1132810063798</v>
       </c>
       <c r="O11" t="n">
-        <v>10.81810490714274</v>
+        <v>10.86799342134415</v>
       </c>
       <c r="P11" t="n">
-        <v>402.2776265058629</v>
+        <v>402.0577897951587</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34026,28 +34270,28 @@
         <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9143652470518032</v>
+        <v>-0.8852464904920408</v>
       </c>
       <c r="J12" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K12" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2580653263956766</v>
+        <v>0.2440017868215597</v>
       </c>
       <c r="M12" t="n">
-        <v>9.702019029814547</v>
+        <v>9.771776594836325</v>
       </c>
       <c r="N12" t="n">
-        <v>149.2777149177131</v>
+        <v>151.8319522777903</v>
       </c>
       <c r="O12" t="n">
-        <v>12.21792596628876</v>
+        <v>12.3220108861253</v>
       </c>
       <c r="P12" t="n">
-        <v>407.9870238718069</v>
+        <v>407.6853027179618</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34104,28 +34348,28 @@
         <v>0.137</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6711336526174073</v>
+        <v>-0.6389466914248191</v>
       </c>
       <c r="J13" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K13" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1724751613251571</v>
+        <v>0.1563813656447401</v>
       </c>
       <c r="M13" t="n">
-        <v>8.889570991103223</v>
+        <v>8.977470021034753</v>
       </c>
       <c r="N13" t="n">
-        <v>133.8901107668628</v>
+        <v>137.3782464528594</v>
       </c>
       <c r="O13" t="n">
-        <v>11.57108943733747</v>
+        <v>11.72084666109319</v>
       </c>
       <c r="P13" t="n">
-        <v>395.848616929695</v>
+        <v>395.5138686319575</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34182,28 +34426,28 @@
         <v>0.1005</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8227082430866598</v>
+        <v>-0.7904452607657576</v>
       </c>
       <c r="J14" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="K14" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2722708405300528</v>
+        <v>0.2518460173226007</v>
       </c>
       <c r="M14" t="n">
-        <v>8.271410865965761</v>
+        <v>8.405013139768524</v>
       </c>
       <c r="N14" t="n">
-        <v>112.7576017025224</v>
+        <v>116.4736189127239</v>
       </c>
       <c r="O14" t="n">
-        <v>10.61873823495628</v>
+        <v>10.79229442300033</v>
       </c>
       <c r="P14" t="n">
-        <v>398.1787874475272</v>
+        <v>397.8447318216564</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34241,7 +34485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O533"/>
+  <dimension ref="A1:O537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74944,7 +75188,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>-40.954792782141226,172.10001836157895</t>
+          <t>-40.95483029298421,172.09978241925666</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -74988,6 +75232,314 @@
         </is>
       </c>
       <c r="O533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:59+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-40.957516663200146,172.10032793355265</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-40.95675896944528,172.10073319905112</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-40.9559788590325,172.10127939087022</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-40.9553159395759,172.10108843248878</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-40.95483029298421,172.09978241925666</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-40.954151090376826,172.09969380162133</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-40.95330040729033,172.10068370140996</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-40.952802108820805,172.09942968294104</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-40.9521367483835,172.09915237260773</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-40.95146664734545,172.0988829793194</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-40.95079846448875,172.09870171559737</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>-40.95011890106217,172.09867178354958</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>-40.94944208531346,172.09860520033806</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-40.95751416738896,172.10034363266786</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-40.95675926525278,172.1007313384385</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-40.95596105445474,172.10139137498837</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-40.95529804266801,172.10120099694265</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-40.95482576360807,172.0998109091023</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-40.95414802149638,172.0997131047483</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-40.95327365459212,172.1008519615867</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-40.9527972334145,172.09946437883647</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-40.9521345536633,172.09917464024437</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-40.95146640742936,172.09888617149932</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-40.95080019718561,172.09867866119333</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>-40.95012185997685,172.09863241412486</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>-40.949446261543955,172.09854963444832</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:18:56+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-40.95751401948897,172.10034456298575</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-40.956760688826,172.1007223842399</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-40.95596273692731,172.1013807928987</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-40.95529909651792,172.10119436866546</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-40.95482604091703,172.09980916482615</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-40.95415201473777,172.0996879874261</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-40.95324939761275,172.1010045235682</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-40.95279780795787,172.09946029009487</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>-40.952132660858815,172.09919384460716</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-40.951465963140066,172.0988920829436</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>-40.95080287174966,172.09864307464952</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>-40.95012402806194,172.09860356685664</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>-40.94944799422744,172.0985265805134</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-40.957513649738964,172.10034688878048</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-40.956765347788,172.10069307958736</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-40.95597248045804,172.10131950979775</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-40.95530750881488,172.10114145872646</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-40.954819977088654,172.0998473063282</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-40.95414144003097,172.09975450180994</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-40.95320567167566,172.1012795302204</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-40.952786448387485,172.0995411303453</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-40.952132660858815,172.09919384460716</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-40.951465963140066,172.0988920829436</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-40.950797531496214,172.0987141295068</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>-40.95012402806194,172.09860356685664</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>-40.94944799422744,172.0985265805134</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
